--- a/output/laminas_comunales/comunal_o_ocup_a_2020_maule.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2020_maule.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
         </is>
       </c>
       <c r="C2">
-        <v>41.8808224278582</v>
+        <v>60.897495086465</v>
       </c>
     </row>
     <row r="3">
@@ -399,22 +399,22 @@
         </is>
       </c>
       <c r="C3">
-        <v>40.7413634051505</v>
+        <v>59.5461466673216</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>7108</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Río Claro</t>
+          <t>Talca</t>
         </is>
       </c>
       <c r="C4">
-        <v>40.4082762438586</v>
+        <v>59.4634470790413</v>
       </c>
     </row>
     <row r="5">
@@ -429,67 +429,67 @@
         </is>
       </c>
       <c r="C5">
-        <v>40.3359957071802</v>
+        <v>59.0862465123913</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Teno</t>
+          <t>Río Claro</t>
         </is>
       </c>
       <c r="C6">
-        <v>40.1020169500853</v>
+        <v>57.7654741624077</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>7306</t>
+          <t>7308</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Romeral</t>
+          <t>Teno</t>
         </is>
       </c>
       <c r="C7">
-        <v>39.843423917335</v>
+        <v>57.2188680285612</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>7101</t>
+          <t>7407</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Talca</t>
+          <t>Villa Alegre</t>
         </is>
       </c>
       <c r="C8">
-        <v>38.0157529998266</v>
+        <v>56.5253925739194</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>San Rafael</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="C9">
-        <v>36.6228070175439</v>
+        <v>56.4340791303249</v>
       </c>
     </row>
     <row r="10">
@@ -504,22 +504,22 @@
         </is>
       </c>
       <c r="C10">
-        <v>36.5650424587522</v>
+        <v>56.260397912441</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Pencahue</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="C11">
-        <v>36.5637813640296</v>
+        <v>55.6467415743189</v>
       </c>
     </row>
     <row r="12">
@@ -534,292 +534,3097 @@
         </is>
       </c>
       <c r="C12">
-        <v>36.515133899159</v>
+        <v>55.4314392099725</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>San Javier</t>
         </is>
       </c>
       <c r="C13">
-        <v>36.179728347761</v>
+        <v>54.4979320872606</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>7102</t>
+          <t>7107</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Constitución</t>
+          <t>Pencahue</t>
         </is>
       </c>
       <c r="C14">
-        <v>36.0064843762923</v>
+        <v>54.1025060386473</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>7406</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>San Javier</t>
+          <t>Constitución</t>
         </is>
       </c>
       <c r="C15">
-        <v>35.2379417075058</v>
+        <v>53.4131143992455</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>7407</t>
+          <t>7105</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Villa Alegre</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="C16">
-        <v>34.3599728042524</v>
+        <v>53.3558188730603</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>7109</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>San Clemente</t>
+          <t>San Rafael</t>
         </is>
       </c>
       <c r="C17">
-        <v>33.6977744854612</v>
+        <v>53.2822757111597</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Yerbas Buenas</t>
+          <t>Curicó</t>
         </is>
       </c>
       <c r="C18">
-        <v>33.5316117542297</v>
+        <v>51.5593886508408</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Pelarco</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="C19">
-        <v>33.356331091052</v>
+        <v>51.3729419410745</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>7402</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Colbún</t>
+          <t>Pelarco</t>
         </is>
       </c>
       <c r="C20">
-        <v>33.1907687008439</v>
+        <v>51.1576354679803</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7403</t>
+          <t>7408</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Longaví</t>
+          <t>Yerbas Buenas</t>
         </is>
       </c>
       <c r="C21">
-        <v>32.2164878904405</v>
+        <v>51.1385944248135</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7404</t>
+          <t>7302</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Parral</t>
+          <t>Hualañé</t>
         </is>
       </c>
       <c r="C22">
-        <v>30.7013200152799</v>
+        <v>50.7360537190083</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7302</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hualañé</t>
+          <t>Río Claro</t>
         </is>
       </c>
       <c r="C23">
-        <v>30.6702387666855</v>
+        <v>50.6852589641434</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7307</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Retiro</t>
+          <t>Sagrada Familia</t>
         </is>
       </c>
       <c r="C24">
-        <v>30.6285227012749</v>
+        <v>50.4093931837074</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7201</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cauquenes</t>
+          <t>San Clemente</t>
         </is>
       </c>
       <c r="C25">
-        <v>29.4623802388412</v>
+        <v>49.8934798452655</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>7306</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Empedrado</t>
+          <t>Romeral</t>
         </is>
       </c>
       <c r="C26">
-        <v>28.9160501769058</v>
+        <v>49.826279877768</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7304</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Licantén</t>
+          <t>Molina</t>
         </is>
       </c>
       <c r="C27">
-        <v>28.6288822098182</v>
+        <v>49.5633632994663</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7103</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Curepto</t>
+          <t>Parral</t>
         </is>
       </c>
       <c r="C28">
-        <v>27.3560209424084</v>
+        <v>49.5349255880941</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>7202</t>
+          <t>7403</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chanco</t>
+          <t>Longaví</t>
         </is>
       </c>
       <c r="C29">
-        <v>26.9167390384573</v>
+        <v>49.5316603048269</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7108</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vichuquén</t>
+          <t>Río Claro</t>
         </is>
       </c>
       <c r="C30">
-        <v>24.5916643199099</v>
+        <v>49.4167129592889</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>49.1832158872518</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>49.1545753530664</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>48.9715275522356</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>48.7221022318215</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>48.6750814051156</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>48.3743970019535</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>48.1765310835675</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>47.8772433456363</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>47.3876240513719</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>47.2904535890786</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>46.5757492690059</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>46.2307252998287</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>45.5014176253114</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>45.3094912999335</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>45.1804519884877</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>45.1031299581711</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>45.0102527124621</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>44.8631489413409</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>44.7523676447757</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>44.7512601358755</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>44.0526896986906</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>43.9738889960769</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>43.6895154246585</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>43.4093839814502</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>43.3875709651257</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>43.1429782478855</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>42.7487562189055</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>42.4663866300465</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>42.4483708703016</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>42.1904646562513</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>41.8808224278582</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>41.8314309009376</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>41.8211710640995</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>41.709093480413</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>41.6448326055313</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>41.495918809445</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>41.2102186620481</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>41.0482180293501</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>40.8957911321179</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>40.7413634051505</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>40.415785764623</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>40.4082762438586</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>40.3359957071802</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>40.3097541986431</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>40.1020169500853</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>40.0793650793651</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>39.843423917335</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>39.7413746919533</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>39.6980155306299</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>39.4557165861514</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>39.4141493396103</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>38.8043707063169</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>38.7795559400231</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>38.7708359842219</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>38.0157529998266</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>37.9112983556231</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>37.8086780400405</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>37.1606562168877</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>37.133532470406</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>36.975828385166</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>36.6228070175439</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>36.5949849441735</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>36.5650424587522</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>36.5637813640296</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>36.5525216353327</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>36.5165234468684</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>36.515133899159</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>36.3376509154873</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>36.2109100274385</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>36.179728347761</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>36.0064843762923</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>35.8807949919012</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>35.8696505692972</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>35.4495538778312</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>35.375545567064</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>35.2379417075058</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>35.1555617378402</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>34.9227729885057</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>34.879345603272</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>7203</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>Pelluhue</t>
         </is>
       </c>
-      <c r="C31">
+      <c r="C110">
+        <v>34.5114052379611</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>34.3599728042524</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>34.0146055539541</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>33.6977744854612</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>33.6728342669609</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>33.5776697739888</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>33.5316117542297</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>33.356331091052</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>33.1907687008439</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>32.9923732615523</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>32.8867754086346</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>32.8498782409397</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>32.7872582480091</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>32.6783334094599</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>32.5460595730866</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>32.5441140923374</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>32.4338909875877</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>32.4270711785298</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>32.4006276150628</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>32.3923513223251</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>32.2164878904405</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>32.1113881961762</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>31.9451146189962</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>31.9333135450678</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>31.8793638785128</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>31.7083868207103</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>31.6631875515898</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>31.6359720451848</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>31.2046528254128</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>31.1321593738883</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>31.1198415021276</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>30.9316935303336</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>30.7256609613817</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>30.7013200152799</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>30.6702387666855</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>30.6285227012749</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>30.5236270753512</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>30.5031446540881</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>30.0475059382423</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>30.0294985250737</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>29.832438317538</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>29.4623802388412</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>29.2342857142857</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>29.1407842570745</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>28.9160501769058</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>28.6288822098182</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>28.4516765285996</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>28.2382027303021</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>27.9448961156278</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>27.3560209424084</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>27.0465088717324</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>26.9911741107248</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>26.9167390384573</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>26.6185222818987</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>26.6178833216186</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>26.5927158439638</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>26.280193236715</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>26.0479673653116</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>25.6944819515708</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>25.5798642763091</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>25.3839531680441</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>25.2795004851707</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>24.5916643199099</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>24.5910120529098</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>24.5792893456216</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>23.9873780837636</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>23.7907129855544</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>23.4648360560769</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>23.3724886430594</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>22.8810264385692</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>22.7942376754816</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C181">
         <v>22.1119363272483</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>22.0806020878854</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>21.5054474879802</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>21.2250286454441</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>21.1908476339054</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>20.9652207893708</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>18.9846096096096</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>7306</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Romeral</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>12.5475382875938</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>7108</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Río Claro</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>12.5266285458011</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>7307</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Sagrada Familia</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>12.5087719298246</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>7308</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Teno</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>12.1107318241706</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>7304</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Molina</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>11.9200294822185</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>San Rafael</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>11.8501036973468</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>7301</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Curicó</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>11.1867770016649</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>7107</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Pencahue</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>10.8883382143125</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>7102</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Constitución</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>10.5658175379291</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>7305</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Rauco</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>10.2691655097948</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Pelarco</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>10.2155203587185</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>7101</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Talca</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>10.1112715096418</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>7109</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>San Clemente</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>10.0350408487242</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>9.90274659907096</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Linares</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>9.65969139716762</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>San Javier</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>9.25866092263507</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>7407</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Villa Alegre</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>9.215413184772521</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>7408</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Yerbas Buenas</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>9.100407747196741</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>7402</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Colbún</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>8.84405756185547</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>7405</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>8.729385002843451</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>7105</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>8.66503175501478</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>7403</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Longaví</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>8.534795491678439</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>7302</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Hualañé</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>8.26366772823779</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>7303</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Licantén</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>8.218503937007871</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Parral</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>7.96001926782274</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>7309</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Vichuquén</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>7.81799899446958</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>7104</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Empedrado</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>7.79079861111111</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Chanco</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>7.6851174510282</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>7201</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Cauquenes</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>7.44616093315565</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>7103</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Curepto</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>6.94969119146129</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>7203</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Pelluhue</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>5.14378290805994</v>
       </c>
     </row>
   </sheetData>
